--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,174 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E8" s="3">
         <v>61700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>101300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>123100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>116200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>119100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>120600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E9" s="3">
         <v>8500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E10" s="3">
         <v>53200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>54800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>59000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>86600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>107300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>99600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>101600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>102700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -872,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,78 +923,87 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>418700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>190300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>24200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>81100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>30500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>31400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>54900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>55300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E17" s="3">
         <v>48300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>474400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>58300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>253600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>177100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>91900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>95300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>93900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E18" s="3">
         <v>13400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-411900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-177700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-54000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>26700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,148 +1106,161 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-137200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-24400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>17300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-53900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-95600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-98400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-405500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>57800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-196000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-52100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>77600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>80400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>82300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>16100</v>
+        <v>16400</v>
       </c>
       <c r="E22" s="3">
         <v>16100</v>
       </c>
       <c r="F22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="G22" s="3">
         <v>17000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>21500</v>
       </c>
       <c r="M22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-139900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-452400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-248100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-119400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-76600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1294,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-139900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-452400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-248100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-119400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-76600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-127600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-416500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-228600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-111200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-72200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>137200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>24400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-17300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>53900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>95600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-127600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-416500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-228600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-111200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-72200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-127600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-416500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-228600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-111200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-72200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,43 +1789,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>391800</v>
+      </c>
+      <c r="E41" s="3">
         <v>364400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>360600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>368200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>233200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>75800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>202700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>184200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>168600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>164100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1774,43 +1863,49 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E43" s="3">
         <v>63900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>69700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>81400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>112500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>109200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>109800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1844,43 +1939,49 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E45" s="3">
         <v>29000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>39000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1914,113 +2015,125 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>50200</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>146400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>164900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>199500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>194500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2093300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2195300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2223200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2769100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2888100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3201100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4435100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4566800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4616300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4664700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E49" s="3">
         <v>125300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>126000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>127500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>128500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>265200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>270100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>271700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>273000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>274400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2205,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E52" s="3">
         <v>22700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>68500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>66200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2789600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2840200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3010200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3584600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3633400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3934400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5149000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5250300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5273000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5311400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,43 +2353,47 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E57" s="3">
         <v>13100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>79100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>80200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>80100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>110800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>103700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>109100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>109600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2294,43 +2427,49 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E59" s="3">
         <v>93200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>88900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>60400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>65300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>66000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>67000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>65700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2364,43 +2503,49 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1435900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1442000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1460500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1461600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1485400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1486800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2529200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2531100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2532400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2534000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2434,8 +2579,11 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1677500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1710900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1750900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1786700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1821900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1861800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2952100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2963400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2990200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3011900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2671,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>125000</v>
@@ -2694,8 +2861,11 @@
       <c r="M70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1903900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1875800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1740000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1315400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-909100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-808500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-780600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-752900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1112100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1129300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1259300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1672900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1686500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1947600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2071900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2162000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2157800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2174500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-127600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-416500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-228600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-111200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-72200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3226,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E83" s="3">
         <v>25400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>31700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>43000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>60400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>53200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>55300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E89" s="3">
         <v>34000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>59500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>55900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>60900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>124200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>165000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>176800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>927800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,8 +3676,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3453,34 +3686,37 @@
         <v>-8100</v>
       </c>
       <c r="E96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F96" s="3">
         <v>-2700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-21800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-28400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-28900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-28700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-28100</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-133200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-55000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-36800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-43600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3654,39 +3902,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E102" s="3">
         <v>6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>132300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>150100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-134400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E8" s="3">
         <v>63100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>61700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>75900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>101300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>123100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>116200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>119100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>120600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E9" s="3">
         <v>7800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E10" s="3">
         <v>55300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>53200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>54800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>59000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>86600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>107300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>101600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>102700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,84 +943,93 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>418700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>190300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>81100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E15" s="3">
         <v>25400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>30500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>31400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>35300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>60000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>52900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>54900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E17" s="3">
         <v>78400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>474400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>58300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>253600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>177100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>91900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>95300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>93900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-15300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-411900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-177700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-54000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>26700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,160 +1140,173 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-137200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-24400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-53900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-95600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E21" s="3">
         <v>20400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-98400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-405500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>57800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-196000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-52100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>77600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>80400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>82300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E22" s="3">
         <v>16400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>16100</v>
       </c>
       <c r="F22" s="3">
         <v>16100</v>
       </c>
       <c r="G22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H22" s="3">
         <v>17000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>21500</v>
       </c>
       <c r="N22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-139900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-452400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-248100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-119400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-76600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-139900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-452400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-248100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-119400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-76600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-127600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-416500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-228600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-111200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-72200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>137200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>24400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>53900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>95600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-127600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-416500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-228600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-111200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-72200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-127600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-416500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-228600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-111200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-72200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>436300</v>
+      </c>
+      <c r="E41" s="3">
         <v>391800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>364400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>360600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>368200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>233200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>75800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>202700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>184200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>168600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>164100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,46 +1956,52 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E43" s="3">
         <v>63300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>69700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>79600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>81400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>111700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>112500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>109200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1942,46 +2038,52 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E45" s="3">
         <v>27400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>39000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2018,122 +2120,134 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E47" s="3">
         <v>50200</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>146400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>164900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>199500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>194500</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2046000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2093300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2195300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2223200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2769100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2888100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3201100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4435100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4566800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4616300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4664700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E49" s="3">
         <v>108300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>125300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>126000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>127500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>128500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>265200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>270100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>271700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>273000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>274400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E52" s="3">
         <v>28300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>68500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>66200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2753800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2789600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2840200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3010200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3584600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3633400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3934400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5149000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5250300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5273000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5311400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,46 +2484,50 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E57" s="3">
         <v>11400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>79100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>80200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>80100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>110800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>103700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>109100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>109600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2430,46 +2564,52 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E59" s="3">
         <v>91600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>93200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>88900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>60400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>65300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>66000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>65700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2506,46 +2646,52 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1416400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1435900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1442000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1460500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1461600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1485400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1486800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2529200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2531100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2532400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2534000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2582,8 +2728,11 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1642800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1677500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1710900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1750900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1786700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1821900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1861800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2952100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2963400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2990200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3011900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2841,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>125000</v>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1907100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1903900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1875800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1740000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1315400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-909100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-808500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-780600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-752900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1110900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1112100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1129300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1259300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1672900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1686500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1947600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2071900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2162000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2157800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2174500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-127600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-416500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-228600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-111200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-72200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E83" s="3">
         <v>25800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>43000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>53200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E89" s="3">
         <v>30400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>59500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>55900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E94" s="3">
         <v>18800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>124200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>165000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>176800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>927800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,46 +3910,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8100</v>
+        <v>-8200</v>
       </c>
       <c r="E96" s="3">
         <v>-8100</v>
       </c>
       <c r="F96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="G96" s="3">
         <v>-2700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-21800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-28400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-28900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-28700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-28100</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-133200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-55000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-44100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-43600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-37700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3905,42 +4154,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E102" s="3">
         <v>30900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>132300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>150100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-134400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,199 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E8" s="3">
         <v>59200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>61700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>62500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>67000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>101300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>123100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>116200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>119100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>120600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E9" s="3">
         <v>7300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E10" s="3">
         <v>51900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>55300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>59000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>65700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>86600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>107300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>99600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>101600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>102700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,90 +963,99 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>418700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>190300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>81100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E15" s="3">
         <v>23400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>31400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>60000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>52900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>54900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E17" s="3">
         <v>50800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>78400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>474400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>253600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>100700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>91900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>95300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>93900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E18" s="3">
         <v>8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-411900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-177700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-54000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,90 +1174,97 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>13200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-137200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-24400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-53900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-95600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E21" s="3">
         <v>45400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-98400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-405500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>57800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-196000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-52100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>77600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>80400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>82300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1232,81 +1272,87 @@
         <v>16100</v>
       </c>
       <c r="E22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F22" s="3">
         <v>16400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>16100</v>
       </c>
       <c r="G22" s="3">
         <v>16100</v>
       </c>
       <c r="H22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I22" s="3">
         <v>17000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>21500</v>
       </c>
       <c r="O22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-139900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-452400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-248100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-119400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-76600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
         <v>5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-139900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-452400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-248100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-119400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-76600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E27" s="3">
         <v>5000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-127600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-416500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-228600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-111200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-72200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>137200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>24400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>53900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>95600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E33" s="3">
         <v>5000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-127600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-416500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-228600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-111200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-72200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E35" s="3">
         <v>5000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-127600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-416500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-228600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-111200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-72200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>446800</v>
+      </c>
+      <c r="E41" s="3">
         <v>436300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>391800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>364400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>360600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>368200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>233200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>75800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>202700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>184200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>168600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>164100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,49 +2049,55 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E43" s="3">
         <v>63500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>63300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>63100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>69700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>81400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>111700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>112500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,49 +2137,55 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>27400</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>29500</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
-        <v>29900</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>31900</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>35300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2123,131 +2225,143 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E47" s="3">
         <v>7600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50200</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>146400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>164900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>199500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>194500</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2016100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2046000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2093300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2195300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2223200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2769100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2888100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3201100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4435100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4566800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4616300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4664700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E49" s="3">
         <v>103000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>108300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>125300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>126000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>127500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>128500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>265200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>270100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>271700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>273000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>274400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E52" s="3">
         <v>29400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>20500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>68500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>66200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2730700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2753800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2789600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2840200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3010200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3584600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3633400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3934400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5149000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5250300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5273000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5311400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,49 +2615,53 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E57" s="3">
         <v>9000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>79100</v>
       </c>
-      <c r="I57" s="3">
-        <v>80200</v>
-      </c>
       <c r="J57" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K57" s="3">
         <v>80100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>110800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>103700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>109100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>109600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2567,49 +2701,55 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E59" s="3">
         <v>88900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>91600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>93200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>88900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>52400</v>
       </c>
-      <c r="I59" s="3">
-        <v>60400</v>
-      </c>
       <c r="J59" s="3">
+        <v>97200</v>
+      </c>
+      <c r="K59" s="3">
         <v>65300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>66000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>65700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2649,49 +2789,55 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1408500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1416400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1435900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1442000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1460500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1461600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1485400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1486800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2529200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2531100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2532400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2534000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1633600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1642800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1677500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1710900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1750900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1786700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1821900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1861800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2952100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2963400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2990200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3011900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3012,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>125000</v>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1919200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1907100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1903900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1875800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1740000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1315400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-909100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-808500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-780600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-752900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1097100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1110900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1112100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1129300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1259300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1672900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1686500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1947600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2071900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2162000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2157800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2174500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E81" s="3">
         <v>5000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-127600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-416500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-228600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-111200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-72200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E83" s="3">
         <v>23800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>35700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>43000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>60400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>53200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>55300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>55600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E89" s="3">
         <v>16200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>59500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>55900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>49200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>60900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E94" s="3">
         <v>60500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>18800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>124200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>165000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>176800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>927800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4144,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E96" s="3">
         <v>-8200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-8100</v>
       </c>
       <c r="F96" s="3">
         <v>-8100</v>
       </c>
       <c r="G96" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="H96" s="3">
         <v>-2700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-21800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-28400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-28900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-28700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-133200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-55000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-44100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-43600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-37700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4157,45 +4406,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E102" s="3">
         <v>46500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>30900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>132300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>150100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-134400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,212 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E8" s="3">
         <v>56000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>59200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63100</v>
       </c>
-      <c r="G8" s="3">
-        <v>61700</v>
-      </c>
       <c r="H8" s="3">
-        <v>62500</v>
+        <v>46400</v>
       </c>
       <c r="I8" s="3">
-        <v>67000</v>
+        <v>45000</v>
       </c>
       <c r="J8" s="3">
+        <v>52300</v>
+      </c>
+      <c r="K8" s="3">
         <v>75900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>101300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>123100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>116200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>119100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>120600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6200</v>
+        <v>11100</v>
       </c>
       <c r="E9" s="3">
-        <v>7300</v>
+        <v>10500</v>
       </c>
       <c r="F9" s="3">
-        <v>7800</v>
+        <v>11600</v>
       </c>
       <c r="G9" s="3">
-        <v>8500</v>
+        <v>12700</v>
       </c>
       <c r="H9" s="3">
-        <v>7700</v>
+        <v>13300</v>
       </c>
       <c r="I9" s="3">
-        <v>8000</v>
+        <v>12900</v>
       </c>
       <c r="J9" s="3">
+        <v>13500</v>
+      </c>
+      <c r="K9" s="3">
         <v>10200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>49800</v>
+        <v>43900</v>
       </c>
       <c r="E10" s="3">
-        <v>51900</v>
+        <v>45400</v>
       </c>
       <c r="F10" s="3">
-        <v>55300</v>
+        <v>47600</v>
       </c>
       <c r="G10" s="3">
-        <v>53200</v>
+        <v>50300</v>
       </c>
       <c r="H10" s="3">
-        <v>54800</v>
+        <v>33100</v>
       </c>
       <c r="I10" s="3">
-        <v>59000</v>
+        <v>32100</v>
       </c>
       <c r="J10" s="3">
+        <v>38900</v>
+      </c>
+      <c r="K10" s="3">
         <v>65700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>86600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>107300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>99600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>101600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>102700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,96 +983,105 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6500</v>
+        <v>27300</v>
       </c>
       <c r="E14" s="3">
-        <v>6000</v>
+        <v>6600</v>
       </c>
       <c r="F14" s="3">
-        <v>28600</v>
+        <v>-3200</v>
       </c>
       <c r="G14" s="3">
-        <v>100</v>
+        <v>23700</v>
       </c>
       <c r="H14" s="3">
-        <v>418700</v>
+        <v>125600</v>
       </c>
       <c r="I14" s="3">
-        <v>3200</v>
+        <v>407100</v>
       </c>
       <c r="J14" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="K14" s="3">
         <v>190300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>24200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>81100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>23000</v>
+        <v>22200</v>
       </c>
       <c r="E15" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F15" s="3">
         <v>23400</v>
       </c>
-      <c r="F15" s="3">
-        <v>25400</v>
-      </c>
       <c r="G15" s="3">
-        <v>25000</v>
+        <v>23400</v>
       </c>
       <c r="H15" s="3">
-        <v>30500</v>
+        <v>24500</v>
       </c>
       <c r="I15" s="3">
+        <v>30000</v>
+      </c>
+      <c r="J15" s="3">
         <v>31400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>60000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>52900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>54900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>55300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>49300</v>
+        <v>43100</v>
       </c>
       <c r="E17" s="3">
-        <v>50800</v>
+        <v>42800</v>
       </c>
       <c r="F17" s="3">
-        <v>78400</v>
+        <v>44900</v>
       </c>
       <c r="G17" s="3">
+        <v>49800</v>
+      </c>
+      <c r="H17" s="3">
         <v>48300</v>
       </c>
-      <c r="H17" s="3">
-        <v>474400</v>
-      </c>
       <c r="I17" s="3">
-        <v>58300</v>
+        <v>55700</v>
       </c>
       <c r="J17" s="3">
+        <v>54900</v>
+      </c>
+      <c r="K17" s="3">
         <v>253600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>100700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>177100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>91900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>95300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>93900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6700</v>
+        <v>11900</v>
       </c>
       <c r="E18" s="3">
-        <v>8400</v>
+        <v>13100</v>
       </c>
       <c r="F18" s="3">
-        <v>-15300</v>
+        <v>14400</v>
       </c>
       <c r="G18" s="3">
-        <v>13400</v>
+        <v>13200</v>
       </c>
       <c r="H18" s="3">
-        <v>-411900</v>
+        <v>-1800</v>
       </c>
       <c r="I18" s="3">
-        <v>8700</v>
+        <v>-10700</v>
       </c>
       <c r="J18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-177700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-54000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,207 +1208,220 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5400</v>
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
-        <v>13200</v>
+        <v>-5200</v>
       </c>
       <c r="F20" s="3">
-        <v>10000</v>
+        <v>-3900</v>
       </c>
       <c r="G20" s="3">
-        <v>-137200</v>
+        <v>-5100</v>
       </c>
       <c r="H20" s="3">
-        <v>-24400</v>
+        <v>-3600</v>
       </c>
       <c r="I20" s="3">
-        <v>17300</v>
+        <v>18600</v>
       </c>
       <c r="J20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-53900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-95600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>35400</v>
+        <v>37100</v>
       </c>
       <c r="E21" s="3">
-        <v>45400</v>
+        <v>40800</v>
       </c>
       <c r="F21" s="3">
-        <v>20400</v>
+        <v>41700</v>
       </c>
       <c r="G21" s="3">
-        <v>-98400</v>
+        <v>41700</v>
       </c>
       <c r="H21" s="3">
-        <v>-405500</v>
+        <v>26300</v>
       </c>
       <c r="I21" s="3">
-        <v>57800</v>
+        <v>700</v>
       </c>
       <c r="J21" s="3">
+        <v>26800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-196000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-52100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>77600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>80400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>82300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F22" s="3">
         <v>16100</v>
       </c>
-      <c r="E22" s="3">
-        <v>16100</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>16100</v>
       </c>
       <c r="H22" s="3">
         <v>16100</v>
       </c>
       <c r="I22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="J22" s="3">
         <v>17000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>21500</v>
       </c>
       <c r="P22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-139900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-452400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-248100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-119400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-76600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-139900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-452400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-248100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-119400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-76600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-127600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-416500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-228600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-111200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-72200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5400</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
-        <v>-13200</v>
+        <v>5200</v>
       </c>
       <c r="F32" s="3">
-        <v>-10000</v>
+        <v>3900</v>
       </c>
       <c r="G32" s="3">
-        <v>137200</v>
+        <v>5100</v>
       </c>
       <c r="H32" s="3">
-        <v>24400</v>
+        <v>3600</v>
       </c>
       <c r="I32" s="3">
-        <v>-17300</v>
+        <v>-18600</v>
       </c>
       <c r="J32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K32" s="3">
         <v>53900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>95600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-127600</v>
       </c>
-      <c r="H33" s="3">
-        <v>-416500</v>
-      </c>
       <c r="I33" s="3">
-        <v>6000</v>
+        <v>-411500</v>
       </c>
       <c r="J33" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-228600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-111200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-72200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-127600</v>
       </c>
-      <c r="H35" s="3">
-        <v>-416500</v>
-      </c>
       <c r="I35" s="3">
-        <v>6000</v>
+        <v>-411500</v>
       </c>
       <c r="J35" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-228600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-111200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-72200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,75 +2050,79 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E41" s="3">
         <v>446800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>436300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>391800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>364400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>360600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>368200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>233200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>75800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>202700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>184200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>168600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>164100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>22700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>26900</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>39700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2052,75 +2142,81 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>65300</v>
+        <v>80300</v>
       </c>
       <c r="E43" s="3">
+        <v>79900</v>
+      </c>
+      <c r="F43" s="3">
         <v>63500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>63900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>69700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>79600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>81400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>111700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>112500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>109800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2140,75 +2236,81 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>36500</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>50200</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>35300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>395500</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>566600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>545600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>541400</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>473700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>467800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>472900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2228,140 +2330,152 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>7600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>50200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>146400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>164900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>199500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>194500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2016100</v>
+        <v>1743600</v>
       </c>
       <c r="E48" s="3">
-        <v>2046000</v>
+        <v>1850600</v>
       </c>
       <c r="F48" s="3">
-        <v>2093300</v>
+        <v>1873400</v>
       </c>
       <c r="G48" s="3">
-        <v>2195300</v>
+        <v>1912800</v>
       </c>
       <c r="H48" s="3">
-        <v>2223200</v>
+        <v>2000400</v>
       </c>
       <c r="I48" s="3">
-        <v>2769100</v>
+        <v>2020100</v>
       </c>
       <c r="J48" s="3">
+        <v>2526500</v>
+      </c>
+      <c r="K48" s="3">
         <v>2888100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3201100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4435100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4566800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4616300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4664700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>102300</v>
+        <v>257800</v>
       </c>
       <c r="E49" s="3">
-        <v>103000</v>
+        <v>267800</v>
       </c>
       <c r="F49" s="3">
-        <v>108300</v>
+        <v>275600</v>
       </c>
       <c r="G49" s="3">
-        <v>125300</v>
+        <v>288800</v>
       </c>
       <c r="H49" s="3">
-        <v>126000</v>
+        <v>320100</v>
       </c>
       <c r="I49" s="3">
-        <v>127500</v>
+        <v>329100</v>
       </c>
       <c r="J49" s="3">
+        <v>370200</v>
+      </c>
+      <c r="K49" s="3">
         <v>128500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>265200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>270100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>271700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>273000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>274400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2565,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>32600</v>
+        <v>30600</v>
       </c>
       <c r="E52" s="3">
-        <v>29400</v>
+        <v>27600</v>
       </c>
       <c r="F52" s="3">
-        <v>28300</v>
+        <v>41000</v>
       </c>
       <c r="G52" s="3">
-        <v>22700</v>
+        <v>27400</v>
       </c>
       <c r="H52" s="3">
-        <v>20500</v>
+        <v>29000</v>
       </c>
       <c r="I52" s="3">
-        <v>22300</v>
+        <v>29500</v>
       </c>
       <c r="J52" s="3">
+        <v>29900</v>
+      </c>
+      <c r="K52" s="3">
         <v>31300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>68500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2659,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2444300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2730700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2753800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2789600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2840200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3010200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3584600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3633400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3934400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5149000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5250300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5273000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5311400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,75 +2746,79 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>9700</v>
-      </c>
-      <c r="E57" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>11400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>13100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>19800</v>
-      </c>
-      <c r="I57" s="3">
-        <v>79100</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>17400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>80100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>110800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>103700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>109100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>109600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2704,75 +2838,81 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>89300</v>
+        <v>10300</v>
       </c>
       <c r="E59" s="3">
-        <v>88900</v>
+        <v>9200</v>
       </c>
       <c r="F59" s="3">
-        <v>91600</v>
+        <v>9200</v>
       </c>
       <c r="G59" s="3">
-        <v>93200</v>
+        <v>9500</v>
       </c>
       <c r="H59" s="3">
-        <v>88900</v>
+        <v>8900</v>
       </c>
       <c r="I59" s="3">
-        <v>52400</v>
+        <v>8900</v>
       </c>
       <c r="J59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K59" s="3">
         <v>97200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>65300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>66000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>65700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>54200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>61400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>48300</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>47700</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>43800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>34900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2792,75 +2932,81 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1408500</v>
+        <v>1214100</v>
       </c>
       <c r="E61" s="3">
-        <v>1416400</v>
+        <v>1436900</v>
       </c>
       <c r="F61" s="3">
-        <v>1435900</v>
+        <v>1444100</v>
       </c>
       <c r="G61" s="3">
-        <v>1442000</v>
+        <v>1479800</v>
       </c>
       <c r="H61" s="3">
-        <v>1460500</v>
+        <v>1487500</v>
       </c>
       <c r="I61" s="3">
-        <v>1461600</v>
+        <v>1505500</v>
       </c>
       <c r="J61" s="3">
+        <v>1505700</v>
+      </c>
+      <c r="K61" s="3">
         <v>1485400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1486800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2529200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2531100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2532400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2534000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>36100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>39400</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>48200</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>53300</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>57400</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3167,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1633600</v>
+        <v>1312200</v>
       </c>
       <c r="E66" s="3">
-        <v>1642800</v>
+        <v>1544100</v>
       </c>
       <c r="F66" s="3">
-        <v>1677500</v>
+        <v>1551900</v>
       </c>
       <c r="G66" s="3">
-        <v>1710900</v>
+        <v>1585900</v>
       </c>
       <c r="H66" s="3">
-        <v>1750900</v>
+        <v>1594900</v>
       </c>
       <c r="I66" s="3">
-        <v>1786700</v>
+        <v>1615400</v>
       </c>
       <c r="J66" s="3">
+        <v>1613500</v>
+      </c>
+      <c r="K66" s="3">
         <v>1821900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1861800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2952100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2963400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2990200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3011900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3183,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>125000</v>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3421,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-1919200</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1907100</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1903900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1875800</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-1740000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-1315400</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-909100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-808500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-780600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-752900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3609,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1047800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1097100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1110900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1112100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1129300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1259300</v>
       </c>
-      <c r="I76" s="3">
-        <v>1672900</v>
-      </c>
       <c r="J76" s="3">
+        <v>1669100</v>
+      </c>
+      <c r="K76" s="3">
         <v>1686500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1947600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2071900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2162000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2157800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2174500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-127600</v>
       </c>
-      <c r="H81" s="3">
-        <v>-416500</v>
-      </c>
       <c r="I81" s="3">
-        <v>6000</v>
+        <v>-411500</v>
       </c>
       <c r="J81" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-228600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-111200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-72200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +3823,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>23400</v>
+        <v>16200</v>
       </c>
       <c r="E83" s="3">
-        <v>23800</v>
+        <v>19500</v>
       </c>
       <c r="F83" s="3">
-        <v>25800</v>
+        <v>20100</v>
       </c>
       <c r="G83" s="3">
-        <v>25400</v>
+        <v>21700</v>
       </c>
       <c r="H83" s="3">
-        <v>30800</v>
+        <v>26100</v>
       </c>
       <c r="I83" s="3">
-        <v>31700</v>
+        <v>32300</v>
       </c>
       <c r="J83" s="3">
+        <v>32100</v>
+      </c>
+      <c r="K83" s="3">
         <v>35700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>43000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>60400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>53200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>55300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>55600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E89" s="3">
         <v>24500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>34000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>59500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>55900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>60900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4171,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E94" s="3">
         <v>7300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>60500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>18800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>124200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>165000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>176800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>927800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,52 +4378,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8300</v>
+        <v>8300</v>
       </c>
       <c r="E96" s="3">
-        <v>-8200</v>
+        <v>8300</v>
       </c>
       <c r="F96" s="3">
-        <v>-8100</v>
+        <v>8200</v>
       </c>
       <c r="G96" s="3">
-        <v>-8100</v>
+        <v>8100</v>
       </c>
       <c r="H96" s="3">
-        <v>-2700</v>
+        <v>8100</v>
       </c>
       <c r="I96" s="3">
-        <v>-21800</v>
+        <v>2700</v>
       </c>
       <c r="J96" s="3">
+        <v>21800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-28400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-28900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,75 +4564,81 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-251800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-28200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-133200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-55000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-44100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-37700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4409,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="E102" s="3">
         <v>13800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>30900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>132300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>150100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-134400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,225 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E8" s="3">
         <v>55000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>59200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>52300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>75900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>101300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>123100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>116200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>119100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>120600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E9" s="3">
         <v>11100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E10" s="3">
         <v>43900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>45400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>32100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>107300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>99600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>101600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>102700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -939,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,102 +1002,111 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E14" s="3">
         <v>27300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>125600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>407100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-30600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>190300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>81100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E15" s="3">
         <v>22200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>23400</v>
       </c>
       <c r="G15" s="3">
         <v>23400</v>
       </c>
       <c r="H15" s="3">
+        <v>24900</v>
+      </c>
+      <c r="I15" s="3">
         <v>24500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>31400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>42600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>60000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>52900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>54900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>55300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E17" s="3">
         <v>43100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>44900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>49800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>55700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>253600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>100700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>177100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>91900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>95300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>93900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>11900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-177700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-54000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,196 +1241,209 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>18600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-53900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-95600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E21" s="3">
         <v>37100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>41700</v>
       </c>
       <c r="G21" s="3">
         <v>41700</v>
       </c>
       <c r="H21" s="3">
+        <v>43200</v>
+      </c>
+      <c r="I21" s="3">
         <v>26300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-196000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-52100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>77600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>82300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E22" s="3">
         <v>14100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>16100</v>
       </c>
       <c r="I22" s="3">
         <v>16100</v>
       </c>
       <c r="J22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K22" s="3">
         <v>17000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>22400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>21500</v>
       </c>
       <c r="Q22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-26500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-139900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-452400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-248100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-119400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-76600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1423,8 +1468,8 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1444,8 +1489,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-26500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-139900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-452400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-248100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-119400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-76600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-127600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-416500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-228600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-111200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-72200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-18600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>53900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>95600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-127600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-411500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-228600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-111200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-72200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-127600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-411500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-228600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-111200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-72200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,82 +2136,86 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E41" s="3">
         <v>241600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>446800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>436300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>391800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>364400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>360600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>368200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>233200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>75800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>202700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>184200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>168600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>164100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E42" s="3">
         <v>12000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>39700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2145,55 +2234,61 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E43" s="3">
         <v>80300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>79900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>63500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>63300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>81400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>111700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>112500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>109200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>109800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2218,8 +2313,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2239,25 +2334,28 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>36500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7600</v>
       </c>
-      <c r="G45" s="3">
-        <v>50200</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="H45" s="3">
+        <v>49700</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -2265,56 +2363,59 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>35300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>40400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>230600</v>
+      </c>
+      <c r="E46" s="3">
         <v>395500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>566600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>545600</v>
       </c>
-      <c r="G46" s="3">
-        <v>541400</v>
-      </c>
       <c r="H46" s="3">
+        <v>540900</v>
+      </c>
+      <c r="I46" s="3">
         <v>473700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>467800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>472900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2333,8 +2434,11 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2353,129 +2457,138 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>146400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>164900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>199500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>194500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2116300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1743600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1850600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1873400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1912800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2000400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2020100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2526500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2888100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3201100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4435100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4566800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4616300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4664700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>277100</v>
+      </c>
+      <c r="E49" s="3">
         <v>257800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>267800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>275600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>288800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>320100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>329100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>370200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>128500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>265200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>270100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>271700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>273000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>274400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2684,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E52" s="3">
         <v>30600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>41000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>68500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2676200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2444300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2730700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2753800</v>
       </c>
-      <c r="G54" s="3">
-        <v>2789600</v>
-      </c>
       <c r="H54" s="3">
+        <v>2789100</v>
+      </c>
+      <c r="I54" s="3">
         <v>2840200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3010200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3584600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3633400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3934400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5149000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5250300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5273000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5311400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,8 +2876,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2773,56 +2903,59 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>17400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>80100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>110800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>103700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>109100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>109600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
         <v>11000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19300</v>
       </c>
-      <c r="G58" s="3">
-        <v>2400</v>
-      </c>
       <c r="H58" s="3">
+        <v>29100</v>
+      </c>
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2841,22 +2974,25 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E59" s="3">
         <v>10300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>9200</v>
       </c>
       <c r="F59" s="3">
         <v>9200</v>
       </c>
       <c r="G59" s="3">
-        <v>9500</v>
+        <v>9200</v>
       </c>
       <c r="H59" s="3">
         <v>8900</v>
@@ -2865,58 +3001,61 @@
         <v>8900</v>
       </c>
       <c r="J59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>97200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>65300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>66000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>65700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E60" s="3">
         <v>54200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61400</v>
       </c>
-      <c r="G60" s="3">
-        <v>48300</v>
-      </c>
       <c r="H60" s="3">
+        <v>74400</v>
+      </c>
+      <c r="I60" s="3">
         <v>47700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34900</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2935,82 +3074,88 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1388900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1214100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1436900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1444100</v>
       </c>
-      <c r="G61" s="3">
-        <v>1479800</v>
-      </c>
       <c r="H61" s="3">
+        <v>1453100</v>
+      </c>
+      <c r="I61" s="3">
         <v>1487500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1505500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1505700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1485400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1486800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2529200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2531100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2532400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2534000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E62" s="3">
         <v>36100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>39400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>48200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>48400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>53300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57400</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3029,8 +3174,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1524200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1312200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1544100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1551900</v>
       </c>
-      <c r="G66" s="3">
-        <v>1585900</v>
-      </c>
       <c r="H66" s="3">
+        <v>1585400</v>
+      </c>
+      <c r="I66" s="3">
         <v>1594900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1615400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1613500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1821900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1861800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2952100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2963400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2990200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3011900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3354,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>125000</v>
@@ -3377,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,8 +3594,11 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3450,29 +3623,32 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-909100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-808500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-780600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-752900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1085200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1047800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1097100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1110900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1112100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1129300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1259300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1669100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1686500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1947600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2071900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2162000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2157800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2174500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-127600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-411500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-228600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-111200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-72200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,55 +4021,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E83" s="3">
         <v>16200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>35700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>43000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>60400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>53200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>55300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>55600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E89" s="3">
         <v>22200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>34000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>59500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>55900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>60900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4198,29 +4418,32 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4539,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-318800</v>
+      </c>
+      <c r="E94" s="3">
         <v>35100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>60500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>124200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>165000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>176800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>927800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4391,43 +4624,46 @@
         <v>8300</v>
       </c>
       <c r="F96" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G96" s="3">
         <v>8200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>8100</v>
       </c>
       <c r="H96" s="3">
         <v>8100</v>
       </c>
       <c r="I96" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J96" s="3">
         <v>2700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>21800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-28400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>174500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-251800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-133200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-55000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-44100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-43600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4640,8 +4888,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4661,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-194600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>46500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>132300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>150100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-134400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E8" s="3">
         <v>57900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>55000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>59200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>63100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>52300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>75900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>101300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>123100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>116200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>119100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>120600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E9" s="3">
         <v>10500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E10" s="3">
         <v>47400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>43900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>33100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>86600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>107300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>99600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>101600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,108 +1022,117 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-15900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>23700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>125600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>407100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-30600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>190300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>24200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>81100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="3">
         <v>25400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22500</v>
       </c>
-      <c r="G15" s="3">
-        <v>23400</v>
-      </c>
       <c r="H15" s="3">
+        <v>22900</v>
+      </c>
+      <c r="I15" s="3">
         <v>24900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>31400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>42600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>60000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>52900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>54900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>55300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E17" s="3">
         <v>45500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>44900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>49800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>253600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>91900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>95300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>93900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E18" s="3">
         <v>12400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-177700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-54000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,208 +1275,221 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>18600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-53900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-95600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E21" s="3">
         <v>39200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40800</v>
       </c>
-      <c r="G21" s="3">
-        <v>41700</v>
-      </c>
       <c r="H21" s="3">
+        <v>41300</v>
+      </c>
+      <c r="I21" s="3">
         <v>43200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-196000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-52100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>77600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>82300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E22" s="3">
         <v>15900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>16100</v>
       </c>
       <c r="J22" s="3">
         <v>16100</v>
       </c>
       <c r="K22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="L22" s="3">
         <v>17000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>22400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>21500</v>
       </c>
       <c r="R22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="E23" s="3">
         <v>13800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-139900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-452400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-248100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-119400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-76600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1471,8 +1517,8 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1492,8 +1538,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="E26" s="3">
         <v>13800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-26500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-139900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-452400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-248100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-119400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-76600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E27" s="3">
         <v>12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-127600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-416500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-228600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-111200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-72200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5200</v>
       </c>
-      <c r="G32" s="3">
-        <v>3900</v>
-      </c>
       <c r="H32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I32" s="3">
         <v>5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-18600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>53900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>95600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E33" s="3">
         <v>12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-127600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-411500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-228600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-111200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-72200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E35" s="3">
         <v>12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-127600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-411500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-228600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-111200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-72200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,88 +2223,92 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E41" s="3">
         <v>146500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>241600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>446800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>436300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>391800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>364400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>360600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>368200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>233200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>75800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>202700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>184200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>168600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>164100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E42" s="3">
         <v>16000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>22700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>39700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>41000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2237,58 +2327,64 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E43" s="3">
         <v>60400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>80300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>79900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>63500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>69700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>81400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>111700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>112500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>109200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>109800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2316,8 +2412,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2337,88 +2433,94 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>36500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>35300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>40400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>380000</v>
+      </c>
+      <c r="E46" s="3">
         <v>230600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>395500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>566600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>545600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>540900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>473700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>467800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>472900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2437,8 +2539,11 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2460,135 +2565,144 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>146400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>164900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>199500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>194500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1934300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2116300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1743600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1850600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1873400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1912800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2000400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2020100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2526500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2888100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3201100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4435100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4566800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4616300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4664700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>247800</v>
+      </c>
+      <c r="E49" s="3">
         <v>277100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>257800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>267800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>275600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>288800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>320100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>329100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>370200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>128500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>265200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>270100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>271700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>273000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>274400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,58 +2804,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E52" s="3">
         <v>38400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>68500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2595200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2676200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2444300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2730700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2753800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2789100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2840200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3010200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3584600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3633400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3934400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5149000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5250300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5273000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5311400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,8 +3007,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2906,29 +3037,32 @@
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>17400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>80100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>110800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>103700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>109100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>109600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2936,29 +3070,29 @@
         <v>2600</v>
       </c>
       <c r="E58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>29100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2977,8 +3111,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2986,16 +3123,16 @@
         <v>9100</v>
       </c>
       <c r="E59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F59" s="3">
         <v>10300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>9200</v>
       </c>
       <c r="G59" s="3">
         <v>9200</v>
       </c>
       <c r="H59" s="3">
-        <v>8900</v>
+        <v>9200</v>
       </c>
       <c r="I59" s="3">
         <v>8900</v>
@@ -3004,61 +3141,64 @@
         <v>8900</v>
       </c>
       <c r="K59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="L59" s="3">
         <v>5400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>97200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>65300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>66000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>67000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>65700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E60" s="3">
         <v>43500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>47700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34900</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3077,88 +3217,94 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1390500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1388900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1214100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1436900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1444100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1453100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1487500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1505500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1505700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1485400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1486800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2529200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2531100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2532400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2534000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E62" s="3">
         <v>82000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>48200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>48400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57400</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1516400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1524200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1312200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1544100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1551900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1585400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1594900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1615400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1613500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1821900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1861800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2952100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2963400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2990200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3011900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3524,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>125000</v>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,8 +3768,11 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3626,29 +3800,32 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-909100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-808500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-780600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-752900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1019200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1085200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1047800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1097100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1110900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1112100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1129300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1259300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1669100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1686500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1947600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2071900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2162000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2157800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2174500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E81" s="3">
         <v>12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-127600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-411500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-228600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-111200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-72200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E83" s="3">
         <v>16300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>20100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>35700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>43000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>60400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>53200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>55300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E89" s="3">
         <v>31700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>34000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>59500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>55900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>49200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>60900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4421,29 +4642,32 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-318800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>35100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>60500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>124200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>165000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>176800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>927800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4627,43 +4861,46 @@
         <v>8300</v>
       </c>
       <c r="G96" s="3">
+        <v>8300</v>
+      </c>
+      <c r="H96" s="3">
         <v>8200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>8100</v>
       </c>
       <c r="I96" s="3">
         <v>8100</v>
       </c>
       <c r="J96" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K96" s="3">
         <v>2700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>21800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E100" s="3">
         <v>174500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-251800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-133200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-55000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-44100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-37700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4891,8 +5140,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-112500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-194600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>46500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>30900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>132300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>150100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-134400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E8" s="3">
         <v>57000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>55000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>63100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>46400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>52300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>75900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>101300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>123100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>116200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>119100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>120600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E9" s="3">
         <v>8800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="3">
         <v>48200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>43900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>86600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>107300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>99600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>101600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>102700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,114 +1042,123 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>287200</v>
+      </c>
+      <c r="E14" s="3">
         <v>52400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-15900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>23700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>125600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>407100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-30600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>190300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>81100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>22900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>30000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>31400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>42600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>60000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>52900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>54900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>55300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E17" s="3">
         <v>42900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>45500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>44900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>48300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>253600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>91900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>95300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>93900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E18" s="3">
         <v>14100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-177700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-54000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,220 +1309,233 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>18600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-53900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-95600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E21" s="3">
         <v>40000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>43200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-196000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-52100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>77600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>80400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>82300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E22" s="3">
         <v>16000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>16100</v>
       </c>
       <c r="K22" s="3">
         <v>16100</v>
       </c>
       <c r="L22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="M22" s="3">
         <v>17000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>22400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>21500</v>
       </c>
       <c r="S22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-286800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-53400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-139900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-452400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-248100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-119400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-76600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1520,8 +1566,8 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1541,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-286800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-53400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-26500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-139900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-452400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-248100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-119400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-76600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-265300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-49400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-127600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-416500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-228600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-111200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-72200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-18600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>53900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>95600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-265300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-49400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-127600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-411500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-228600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-111200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-72200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-265300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-49400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-127600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-411500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-228600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-111200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-72200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,94 +2310,98 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>264400</v>
+      </c>
+      <c r="E41" s="3">
         <v>204000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>146500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>241600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>446800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>436300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>391800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>364400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>360600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>368200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>233200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>75800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>202700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>184200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>168600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>164100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>4600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>16000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>39700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>41000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2330,61 +2420,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E43" s="3">
         <v>54600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>80300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>69700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>81400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>111700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>112500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>109200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>109800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2415,8 +2511,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2436,94 +2532,100 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E45" s="3">
         <v>108900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>36500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49700</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>35300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>334200</v>
+      </c>
+      <c r="E46" s="3">
         <v>380000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>230600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>395500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>566600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>545600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>540900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>473700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>467800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>472900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2542,8 +2644,11 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2568,141 +2673,150 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>146400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>164900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>199500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>194500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1618500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1934300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2116300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1743600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1850600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1873400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1912800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2020100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2526500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2888100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3201100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4435100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4566800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4616300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4664700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>203900</v>
+      </c>
+      <c r="E49" s="3">
         <v>247800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>277100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>257800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>267800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>275600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>288800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>320100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>329100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>370200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>128500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>265200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>270100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>271700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>273000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>274400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E52" s="3">
         <v>20200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>68500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>62000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>66200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2190600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2595200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2676200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2444300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2730700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2753800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2789100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2840200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3010200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3584600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3633400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3934400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5149000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5250300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5273000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5311400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,8 +3138,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3040,62 +3171,65 @@
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>17400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>80100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>110800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>103700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>109100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>109600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2600</v>
+        <v>6000</v>
       </c>
       <c r="E58" s="3">
         <v>2600</v>
       </c>
       <c r="F58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G58" s="3">
         <v>11000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3114,28 +3248,31 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="E59" s="3">
         <v>9100</v>
       </c>
       <c r="F59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G59" s="3">
         <v>10300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>9200</v>
       </c>
       <c r="H59" s="3">
         <v>9200</v>
       </c>
       <c r="I59" s="3">
-        <v>8900</v>
+        <v>9200</v>
       </c>
       <c r="J59" s="3">
         <v>8900</v>
@@ -3144,64 +3281,67 @@
         <v>8900</v>
       </c>
       <c r="L59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="M59" s="3">
         <v>5400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>65300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>66000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>65700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E60" s="3">
         <v>41900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>61000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>61400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>47700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34900</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3220,94 +3360,100 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1292200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1390500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1388900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1214100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1436900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1444100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1453100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1487500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1505500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1505700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1485400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1486800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2529200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2531100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2532400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2534000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E62" s="3">
         <v>74700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>48200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>48400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>57400</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1414300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1516400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1524200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1312200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1544100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1551900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1585400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1594900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1615400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1613500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1821900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1861800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2952100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2963400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2990200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3011900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3695,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>125000</v>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,8 +3942,11 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3803,29 +3977,32 @@
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-909100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-808500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-780600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-752900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>740300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1019200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1085200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1047800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1097100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1110900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1112100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1129300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1259300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1669100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1686500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1947600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2071900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2162000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2157800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2174500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-265300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-49400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-127600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-411500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-228600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-111200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-72200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E83" s="3">
         <v>15600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>35700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>43000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>60400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>53200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>55300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>55600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E89" s="3">
         <v>20200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>34000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>59500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>55900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>49200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>60900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4645,29 +4866,32 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>150300</v>
+      </c>
+      <c r="E94" s="3">
         <v>46900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-318800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>35100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>60500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>18800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>124200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>165000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>176800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>927800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,13 +5079,14 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="E96" s="3">
         <v>8300</v>
@@ -4864,43 +5098,46 @@
         <v>8300</v>
       </c>
       <c r="H96" s="3">
+        <v>8300</v>
+      </c>
+      <c r="I96" s="3">
         <v>8200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>8100</v>
       </c>
       <c r="J96" s="3">
         <v>8100</v>
       </c>
       <c r="K96" s="3">
+        <v>8100</v>
+      </c>
+      <c r="L96" s="3">
         <v>2700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>21800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-109100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>174500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-251800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-133200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-55000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-44100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-43600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-37700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5143,8 +5392,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E102" s="3">
         <v>57800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-112500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-194600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>46500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>132300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>150100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-134400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>34300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>PKST</t>
   </si>
@@ -656,276 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25800</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>57000</v>
       </c>
-      <c r="G8" s="3">
-        <v>57900</v>
-      </c>
       <c r="H8" s="3">
+        <v>29800</v>
+      </c>
+      <c r="I8" s="3">
         <v>26700</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>59200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>46400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>52300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>101300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>123100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>116200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>119100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>120600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>118800</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
         <v>8800</v>
       </c>
-      <c r="G9" s="3">
-        <v>10500</v>
-      </c>
       <c r="H9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>11600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E10" s="3">
         <v>22500</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
         <v>48200</v>
       </c>
-      <c r="G10" s="3">
-        <v>47400</v>
-      </c>
       <c r="H10" s="3">
+        <v>24400</v>
+      </c>
+      <c r="I10" s="3">
         <v>20700</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>47600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>50300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>65700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>86600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>107300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>99600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>101600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>102700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,126 +1081,135 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-6600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>52400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-15900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>27300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-3200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>23700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>125600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>407100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-30600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>190300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>81100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E15" s="3">
         <v>13100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25000</v>
       </c>
-      <c r="G15" s="3">
-        <v>25400</v>
-      </c>
       <c r="H15" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I15" s="3">
         <v>10700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>22500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>30000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>31400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>35300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>42600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>60000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>52900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>54900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>55300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>55100</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E17" s="3">
         <v>24600</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3">
         <v>42900</v>
       </c>
-      <c r="G17" s="3">
-        <v>45500</v>
-      </c>
       <c r="H17" s="3">
+        <v>28400</v>
+      </c>
+      <c r="I17" s="3">
         <v>26000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>44900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>253600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>177100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>91900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>95300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>93900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1200</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3">
         <v>14100</v>
       </c>
-      <c r="G18" s="3">
-        <v>12400</v>
-      </c>
       <c r="H18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I18" s="3">
         <v>700</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>14400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-177700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-54000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,244 +1376,257 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>18600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-53900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-95600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E21" s="3">
         <v>16100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>21300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40000</v>
       </c>
-      <c r="G21" s="3">
-        <v>39200</v>
-      </c>
       <c r="H21" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I21" s="3">
         <v>14500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>41300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>43200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-196000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-52100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>77600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>80400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>82300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16700</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>16000</v>
       </c>
-      <c r="G22" s="3">
-        <v>15900</v>
-      </c>
       <c r="H22" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I22" s="3">
         <v>12600</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>16100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>16100</v>
       </c>
       <c r="M22" s="3">
         <v>16100</v>
       </c>
       <c r="N22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="O22" s="3">
         <v>17000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>21500</v>
       </c>
       <c r="U22" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7000</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3">
         <v>-53400</v>
       </c>
-      <c r="G23" s="3">
-        <v>13800</v>
-      </c>
       <c r="H23" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-36100</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-139900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-452400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-248100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-119400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-76600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1618,8 +1663,8 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1639,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7000</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3">
         <v>-53400</v>
       </c>
-      <c r="G26" s="3">
-        <v>13800</v>
-      </c>
       <c r="H26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-36100</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>5500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-139900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-452400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-248100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-119400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-76600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
         <v>3500</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="E27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3">
         <v>-49400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24400</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-127600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-416500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-228600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-111200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-72200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,17 +1932,20 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E29" s="3">
         <v>10000</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -1893,11 +1953,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I29" s="3">
         <v>8800</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-18600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>53900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>95600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="E33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3">
         <v>-49400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24400</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-127600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-411500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-228600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-111200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-72200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="E35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3">
         <v>-49400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24400</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-127600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-411500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-228600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-111200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-72200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>138700</v>
+      </c>
+      <c r="E41" s="3">
         <v>326100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>264400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>204000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>146500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>241600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>446800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>436300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>391800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>364400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>360600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>368200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>233200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>75800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>202700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>184200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>168600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>164100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>134000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2469,35 +2558,35 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>4600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>16000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>27000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>41000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>33000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2516,67 +2605,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E43" s="3">
         <v>17400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>54500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>54600</v>
       </c>
-      <c r="G43" s="3">
-        <v>60400</v>
-      </c>
       <c r="H43" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I43" s="3">
         <v>80300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>81400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>111700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>112500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>109200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>109800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>105200</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2613,8 +2708,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2634,106 +2729,112 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>475900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>108900</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H45" s="3">
+        <v>1101400</v>
+      </c>
+      <c r="I45" s="3">
         <v>36500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>35300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>35400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>40400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E46" s="3">
         <v>827400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>334200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>380000</v>
       </c>
-      <c r="G46" s="3">
-        <v>230600</v>
-      </c>
       <c r="H46" s="3">
+        <v>1294500</v>
+      </c>
+      <c r="I46" s="3">
         <v>395500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>566600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>545600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>540900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>473700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>467800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>472900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -2752,8 +2853,11 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2784,153 +2888,162 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>146400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>164900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>199500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>194500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1041000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1011300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1618500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1934300</v>
       </c>
-      <c r="G48" s="3">
-        <v>2116300</v>
-      </c>
       <c r="H48" s="3">
+        <v>1187300</v>
+      </c>
+      <c r="I48" s="3">
         <v>1743600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1850600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1873400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1912800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2000400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2020100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2526500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2888100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3201100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4435100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4566800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4616300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4664700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4716500</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E49" s="3">
         <v>125700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>203900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>247800</v>
       </c>
-      <c r="G49" s="3">
-        <v>277100</v>
-      </c>
       <c r="H49" s="3">
+        <v>153100</v>
+      </c>
+      <c r="I49" s="3">
         <v>257800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>267800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>275600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>288800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>320100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>329100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>370200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>128500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>265200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>270100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>271700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>273000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>274400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>275900</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,67 +3163,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E52" s="3">
         <v>18200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20200</v>
       </c>
-      <c r="G52" s="3">
-        <v>38400</v>
-      </c>
       <c r="H52" s="3">
+        <v>36300</v>
+      </c>
+      <c r="I52" s="3">
         <v>30600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>38300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>68500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>62500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>62000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>66200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1352800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1986400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2190600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2595200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2676200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2444300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2730700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2753800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2789100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2840200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3010200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3584600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3633400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3934400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5149000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5250300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5273000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5311400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5335500</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,8 +3399,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3308,68 +3438,71 @@
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>17400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>80100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>110800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>103700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>109100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>109600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>150200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2600</v>
       </c>
       <c r="G58" s="3">
         <v>2600</v>
       </c>
       <c r="H58" s="3">
+        <v>150000</v>
+      </c>
+      <c r="I58" s="3">
         <v>11000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>29100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3388,34 +3521,37 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E59" s="3">
         <v>70300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>9100</v>
       </c>
       <c r="G59" s="3">
         <v>9100</v>
       </c>
       <c r="H59" s="3">
+        <v>77300</v>
+      </c>
+      <c r="I59" s="3">
         <v>10300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>9200</v>
       </c>
       <c r="J59" s="3">
         <v>9200</v>
       </c>
       <c r="K59" s="3">
-        <v>8900</v>
+        <v>9200</v>
       </c>
       <c r="L59" s="3">
         <v>8900</v>
@@ -3424,70 +3560,73 @@
         <v>8900</v>
       </c>
       <c r="N59" s="3">
+        <v>8900</v>
+      </c>
+      <c r="O59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>97200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>65300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>66000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>67000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>65700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>70200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E60" s="3">
         <v>250300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>40800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41900</v>
       </c>
-      <c r="G60" s="3">
-        <v>43500</v>
-      </c>
       <c r="H60" s="3">
+        <v>256800</v>
+      </c>
+      <c r="I60" s="3">
         <v>54200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>61000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>61400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>74400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34900</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -3506,106 +3645,112 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>477300</v>
+      </c>
+      <c r="E61" s="3">
         <v>894300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1296800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1390500</v>
       </c>
-      <c r="G61" s="3">
-        <v>1388900</v>
-      </c>
       <c r="H61" s="3">
+        <v>1195400</v>
+      </c>
+      <c r="I61" s="3">
         <v>1214100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1436900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1444100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1453100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1487500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1505500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1505700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1485400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1486800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2529200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2531100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2532400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2534000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2537000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E62" s="3">
         <v>62600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>68900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>74700</v>
       </c>
-      <c r="G62" s="3">
-        <v>82000</v>
-      </c>
       <c r="H62" s="3">
+        <v>68600</v>
+      </c>
+      <c r="I62" s="3">
         <v>36100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>39400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>48200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>53300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>57400</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -3624,8 +3769,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>574100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1209500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1414300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1516400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1524200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1312200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1544100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1551900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1585400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1594900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1615400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1613500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1821900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1861800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2952100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2963400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2990200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3011900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3017400</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>125000</v>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>125000</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,8 +4289,11 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4157,29 +4330,32 @@
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>-1306600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1049300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-909100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-808500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-780600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-752900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-726600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>745400</v>
+      </c>
+      <c r="E76" s="3">
         <v>741100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>740300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1019200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1085200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1047800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1097100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1110900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1112100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1129300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1259300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1669100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1686500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1947600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2071900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2162000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2157800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2174500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2193100</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="E81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3">
         <v>-49400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24400</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-127600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-411500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-228600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-111200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-72200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>10400</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>15600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>32300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>35700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>60400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>53200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>55300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>55600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>400</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>20200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>16200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>34000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>59500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>55900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>49200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>60900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5093,29 +5313,32 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>383800</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>46900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-318800</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>60500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>18800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>124200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>165000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>176800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>927800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>11700</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,67 +5546,71 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
+      <c r="D96" s="3">
+        <v>3700</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
-        <v>8300</v>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
         <v>8300</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
+      <c r="H96" s="3">
+        <v>8300</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>8200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>8100</v>
       </c>
       <c r="L96" s="3">
         <v>8100</v>
       </c>
       <c r="M96" s="3">
+        <v>8100</v>
+      </c>
+      <c r="N96" s="3">
         <v>2700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>21800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-28400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-28700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-28100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5792,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>-571900</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-9300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>174500</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>-30300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-133200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-55000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-44100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1082100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-43600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-37700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5647,8 +5895,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5668,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-187800</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>57800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-112500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>46500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>132300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>150100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-134400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>34300</v>
       </c>
     </row>
